--- a/artfynd/A 62349-2023 artfynd.xlsx
+++ b/artfynd/A 62349-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62349-2023 artfynd.xlsx
+++ b/artfynd/A 62349-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72065962</v>
+        <v>102616330</v>
       </c>
       <c r="B2" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,23 +712,23 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västerviksvägen/Målenvägen, Äsperyd, Sk</t>
+          <t>DFI P2, Raslången, Skånesidan, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463429</v>
+        <v>463278</v>
       </c>
       <c r="R2" t="n">
-        <v>6234455</v>
+        <v>6234645</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-13</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>01:17</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-06-13</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>01:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,611 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Ulrika Tollgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118415886</v>
+      </c>
+      <c r="B3" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>DFI P2, Raslången, Skånesidan, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>463278</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6234645</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulrika Tollgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulrika Tollgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>72065962</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57754</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västerviksvägen/Målenvägen, Äsperyd, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>463429</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6234455</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-06-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>01:17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-06-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>01:22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulrika Tollgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Ulrika Tollgren, Adrian Tollgren</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118908033</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>DFI P2, Raslången, Skånesidan, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>463278</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6234645</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Tollgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Tollgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>102446121</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43219</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201028</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Thymelicus lineola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>DFI P2, Raslången, Skånesidan, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>463278</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6234645</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-07-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-07-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulrika Tollgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Tollgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118907847</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>DFI P2, Raslången, Skånesidan, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>463278</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6234645</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulrika Tollgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Tollgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62349-2023 artfynd.xlsx
+++ b/artfynd/A 62349-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102616330</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118415886</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72065962</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118908033</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1271,6 +1296,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102446121</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1392,8 +1422,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118907847</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>